--- a/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>2926.5603118846607</v>
+        <v>9.0545881903381087E-10</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>17073.439688115341</v>
+        <v>19999.999999999094</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -4007,423 +4007,453 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="19"/>
-      <c r="B107" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A107" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B107" s="24">
+        <f t="shared" si="12"/>
+        <v>106</v>
       </c>
       <c r="C107" s="20"/>
-      <c r="D107" s="21" t="str">
+      <c r="D107" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E107" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E107" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F107" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G107" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H107" s="21" t="str">
+        <v>9.1138412871548926</v>
+      </c>
+      <c r="F107" s="21">
+        <f t="shared" si="14"/>
+        <v>190.88615871284512</v>
+      </c>
+      <c r="G107" s="21">
+        <f t="shared" si="13"/>
+        <v>2735.6741531718158</v>
+      </c>
+      <c r="H107" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>17264.325846828186</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2"/>
-      <c r="B108" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A108" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B108" s="23">
+        <f t="shared" si="12"/>
+        <v>107</v>
       </c>
       <c r="C108" s="3"/>
-      <c r="D108" s="4" t="str">
+      <c r="D108" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E108" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E108" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F108" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G108" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H108" s="4" t="str">
+        <v>8.5193870579498281</v>
+      </c>
+      <c r="F108" s="4">
+        <f t="shared" si="14"/>
+        <v>191.48061294205019</v>
+      </c>
+      <c r="G108" s="4">
+        <f t="shared" si="13"/>
+        <v>2544.1935402297654</v>
+      </c>
+      <c r="H108" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>17455.806459770236</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="19"/>
-      <c r="B109" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A109" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B109" s="24">
+        <f t="shared" si="12"/>
+        <v>108</v>
       </c>
       <c r="C109" s="20"/>
-      <c r="D109" s="21" t="str">
+      <c r="D109" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E109" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E109" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F109" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G109" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H109" s="21" t="str">
+        <v>7.9230815901164489</v>
+      </c>
+      <c r="F109" s="21">
+        <f t="shared" si="14"/>
+        <v>192.07691840988355</v>
+      </c>
+      <c r="G109" s="21">
+        <f t="shared" si="13"/>
+        <v>2352.1166218198819</v>
+      </c>
+      <c r="H109" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>17647.883378180119</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="2"/>
-      <c r="B110" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A110" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B110" s="23">
+        <f t="shared" si="12"/>
+        <v>109</v>
       </c>
       <c r="C110" s="3"/>
-      <c r="D110" s="4" t="str">
+      <c r="D110" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E110" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E110" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F110" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G110" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H110" s="4" t="str">
+        <v>7.3249191185608415</v>
+      </c>
+      <c r="F110" s="4">
+        <f t="shared" si="14"/>
+        <v>192.67508088143916</v>
+      </c>
+      <c r="G110" s="4">
+        <f t="shared" si="13"/>
+        <v>2159.4415409384428</v>
+      </c>
+      <c r="H110" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>17840.558459061558</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="19"/>
-      <c r="B111" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A111" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B111" s="24">
+        <f t="shared" si="12"/>
+        <v>110</v>
       </c>
       <c r="C111" s="20"/>
-      <c r="D111" s="21" t="str">
+      <c r="D111" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E111" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E111" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F111" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G111" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H111" s="21" t="str">
+        <v>6.7248938602355404</v>
+      </c>
+      <c r="F111" s="21">
+        <f t="shared" si="14"/>
+        <v>193.27510613976446</v>
+      </c>
+      <c r="G111" s="21">
+        <f t="shared" si="13"/>
+        <v>1966.1664347986784</v>
+      </c>
+      <c r="H111" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>18033.833565201323</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2"/>
-      <c r="B112" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A112" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B112" s="23">
+        <f t="shared" si="12"/>
+        <v>111</v>
       </c>
       <c r="C112" s="3"/>
-      <c r="D112" s="4" t="str">
+      <c r="D112" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E112" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E112" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F112" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G112" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H112" s="4" t="str">
+        <v>6.123000014083618</v>
+      </c>
+      <c r="F112" s="4">
+        <f t="shared" si="14"/>
+        <v>193.87699998591637</v>
+      </c>
+      <c r="G112" s="4">
+        <f t="shared" si="13"/>
+        <v>1772.289434812762</v>
+      </c>
+      <c r="H112" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>18227.710565187237</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="19"/>
-      <c r="B113" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A113" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B113" s="24">
+        <f t="shared" si="12"/>
+        <v>112</v>
       </c>
       <c r="C113" s="20"/>
-      <c r="D113" s="21" t="str">
+      <c r="D113" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E113" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E113" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F113" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G113" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H113" s="21" t="str">
+        <v>5.5192317609825992</v>
+      </c>
+      <c r="F113" s="21">
+        <f t="shared" si="14"/>
+        <v>194.48076823901741</v>
+      </c>
+      <c r="G113" s="21">
+        <f t="shared" si="13"/>
+        <v>1577.8086665737446</v>
+      </c>
+      <c r="H113" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>18422.191333426257</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="2"/>
-      <c r="B114" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A114" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B114" s="23">
+        <f t="shared" si="12"/>
+        <v>113</v>
       </c>
       <c r="C114" s="3"/>
-      <c r="D114" s="4" t="str">
+      <c r="D114" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E114" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E114" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F114" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G114" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H114" s="4" t="str">
+        <v>4.9135832636882046</v>
+      </c>
+      <c r="F114" s="4">
+        <f t="shared" si="14"/>
+        <v>195.0864167363118</v>
+      </c>
+      <c r="G114" s="4">
+        <f t="shared" si="13"/>
+        <v>1382.7222498374329</v>
+      </c>
+      <c r="H114" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>18617.277750162568</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="19"/>
-      <c r="B115" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A115" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B115" s="24">
+        <f t="shared" si="12"/>
+        <v>114</v>
       </c>
       <c r="C115" s="20"/>
-      <c r="D115" s="21" t="str">
+      <c r="D115" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E115" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E115" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F115" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G115" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H115" s="21" t="str">
+        <v>4.3060486667779134</v>
+      </c>
+      <c r="F115" s="21">
+        <f t="shared" si="14"/>
+        <v>195.69395133322209</v>
+      </c>
+      <c r="G115" s="21">
+        <f t="shared" si="13"/>
+        <v>1187.0282985042109</v>
+      </c>
+      <c r="H115" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>18812.97170149579</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="2"/>
-      <c r="B116" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A116" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B116" s="23">
+        <f t="shared" si="12"/>
+        <v>115</v>
       </c>
       <c r="C116" s="3"/>
-      <c r="D116" s="4" t="str">
+      <c r="D116" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E116" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E116" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F116" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G116" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H116" s="4" t="str">
+        <v>3.6966220965943535</v>
+      </c>
+      <c r="F116" s="4">
+        <f t="shared" si="14"/>
+        <v>196.30337790340565</v>
+      </c>
+      <c r="G116" s="4">
+        <f t="shared" si="13"/>
+        <v>990.72492060080526</v>
+      </c>
+      <c r="H116" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>19009.275079399195</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="19"/>
-      <c r="B117" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A117" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B117" s="24">
+        <f t="shared" si="12"/>
+        <v>116</v>
       </c>
       <c r="C117" s="20"/>
-      <c r="D117" s="21" t="str">
+      <c r="D117" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E117" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E117" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F117" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G117" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H117" s="21" t="str">
+        <v>3.0852976611885139</v>
+      </c>
+      <c r="F117" s="21">
+        <f t="shared" si="14"/>
+        <v>196.91470233881148</v>
+      </c>
+      <c r="G117" s="21">
+        <f t="shared" si="13"/>
+        <v>793.81021826199378</v>
+      </c>
+      <c r="H117" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>19206.189781738005</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="2"/>
-      <c r="B118" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A118" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B118" s="23">
+        <f t="shared" si="12"/>
+        <v>117</v>
       </c>
       <c r="C118" s="3"/>
-      <c r="D118" s="4" t="str">
+      <c r="D118" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E118" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E118" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F118" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G118" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H118" s="4" t="str">
+        <v>2.4720694502627842</v>
+      </c>
+      <c r="F118" s="4">
+        <f t="shared" si="14"/>
+        <v>197.52793054973722</v>
+      </c>
+      <c r="G118" s="4">
+        <f t="shared" si="13"/>
+        <v>596.28228771225656</v>
+      </c>
+      <c r="H118" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>19403.717712287744</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="19"/>
-      <c r="B119" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A119" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B119" s="24">
+        <f t="shared" si="12"/>
+        <v>118</v>
       </c>
       <c r="C119" s="20"/>
-      <c r="D119" s="21" t="str">
+      <c r="D119" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E119" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E119" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F119" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G119" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H119" s="21" t="str">
+        <v>1.8569315351138109</v>
+      </c>
+      <c r="F119" s="21">
+        <f t="shared" si="14"/>
+        <v>198.1430684648862</v>
+      </c>
+      <c r="G119" s="21">
+        <f t="shared" si="13"/>
+        <v>398.13921924737036</v>
+      </c>
+      <c r="H119" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>19601.860780752631</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="2"/>
-      <c r="B120" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A120" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B120" s="23">
+        <f t="shared" si="12"/>
+        <v>119</v>
       </c>
       <c r="C120" s="3"/>
-      <c r="D120" s="4" t="str">
+      <c r="D120" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E120" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E120" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F120" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G120" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H120" s="4" t="str">
+        <v>1.23987796857518</v>
+      </c>
+      <c r="F120" s="4">
+        <f t="shared" si="14"/>
+        <v>198.76012203142483</v>
+      </c>
+      <c r="G120" s="4">
+        <f t="shared" si="13"/>
+        <v>199.37909721594554</v>
+      </c>
+      <c r="H120" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>19800.620902784056</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="19"/>
-      <c r="B121" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A121" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B121" s="24">
+        <f t="shared" si="12"/>
+        <v>120</v>
       </c>
       <c r="C121" s="20"/>
-      <c r="D121" s="21" t="str">
+      <c r="D121" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E121" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E121" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F121" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G121" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H121" s="21" t="str">
+        <v>0.62090278495991857</v>
+      </c>
+      <c r="F121" s="21">
+        <f t="shared" si="14"/>
+        <v>199.37909721504008</v>
+      </c>
+      <c r="G121" s="21">
+        <f t="shared" si="13"/>
+        <v>9.0545881903381087E-10</v>
+      </c>
+      <c r="H121" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>19999.999999999094</v>
       </c>
     </row>
   </sheetData>
